--- a/content/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Summary_Stats.xlsx
+++ b/content/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Summary_Stats.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,128 +417,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Number of Observations</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data Start Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data End Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Annual Mean Return (Arithmetic)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Annualized Volatility</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Annualized Sharpe Ratio</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CAGR (Geometric)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Daily Max Return</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Daily Max Return (Date)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Daily Min Return</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Daily Min Return (Date)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Max Drawdown</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Trough</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Recovery Date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Calendar Days to Recovery</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>MAR Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05747230042821247</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.06003419719111461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9573260427761444</v>
+        <v>8976</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1990-01-02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>0.05723511992545527</v>
+        <v>0.07026988067254776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02879420493358031</v>
-      </c>
-      <c r="G2" s="2" t="n">
+        <v>0.06046743461198631</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.162111161544438</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07081979125269311</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.02877350739457318</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>43914</v>
       </c>
-      <c r="H2" t="n">
-        <v>-0.02985179453546805</v>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="K2" t="n">
+        <v>-0.02982880819795986</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>43902</v>
       </c>
-      <c r="J2" t="n">
-        <v>-0.1538209243972309</v>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" t="n">
+        <v>-0.1514261623014011</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>39525</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>39764</v>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>40092</v>
-      </c>
-      <c r="N2" t="n">
-        <v>328</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.3720892989672193</v>
+      <c r="P2" s="1" t="n">
+        <v>40072</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>308</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4676853073231311</v>
       </c>
     </row>
   </sheetData>
